--- a/Dashboards/data/Data final/ingresos/ingresos_sexo_etnia.xlsx
+++ b/Dashboards/data/Data final/ingresos/ingresos_sexo_etnia.xlsx
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>212.47</v>
+        <v>214.58</v>
       </c>
     </row>
     <row r="37">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>202.71</v>
+        <v>207.44</v>
       </c>
     </row>
     <row r="38">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>228.92</v>
+        <v>231.02</v>
       </c>
     </row>
     <row r="39">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>215.78</v>
+        <v>216.81</v>
       </c>
     </row>
     <row r="40">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>225.38</v>
+        <v>223.94</v>
       </c>
     </row>
     <row r="41">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>214.51</v>
+        <v>217.04</v>
       </c>
     </row>
     <row r="42">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>227.82</v>
+        <v>215.89</v>
       </c>
     </row>
     <row r="43">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>211.91</v>
+        <v>206.44</v>
       </c>
     </row>
     <row r="44">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>239.7</v>
+        <v>248.54</v>
       </c>
     </row>
     <row r="45">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>227.03</v>
+        <v>242.26</v>
       </c>
     </row>
     <row r="46">
